--- a/408/OS/2024/ModularAutomation/reports/testcases_test.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/testcases_test.xlsx
@@ -1,23 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RjDir\admin_d95c8884-f44c-4529-8f3b-48d5788371c1\Downloads\业务文档\NPEE\408\OS\2024\ModularAutomation\reports\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22185" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="#TEMP" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TEMP'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TEMP'!$A$1:$D$3</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -35,7 +43,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -46,7 +53,6 @@
         <sz val="11"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -60,34 +66,45 @@
     <t>#END_OF_ROW</t>
   </si>
   <si>
-    <t>#END_OF_COL</t>
+    <t>/cgi-bin/luci/api/cmd</t>
   </si>
   <si>
-    <t>/cgi-bin/luci/api/auth</t>
-  </si>
-  <si>
-    <t>login</t>
+    <t>devSta.set</t>
   </si>
   <si>
     <t>{
-    "password": "总之是错误的密码",
-    "username": "admin",
-    "time": "1712643931",
-    "encry": true,
-    "limit": false,
-    "setInit": true
+    "module":"wifi_deassociation",
+    "noParse":true,
+    "async":null,
+    "remoteIp":false,
+    "data":{
+        "user":"hacker",
+        "macs":[
+            "66:77:88:99:AA:BB",
+            "CC:DD:EE:FF:00:11"
+        ]
+    },
+    "device":"pc"
 }</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>#results↓</t>
+  </si>
+  <si>
+    <t>#END_OF_COL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,42 +116,162 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -147,8 +284,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -156,12 +479,257 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -174,30 +742,71 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
-      <color rgb="FFFF0000"/>
-      <color rgb="FF000000"/>
+      <color rgb="00FF0000"/>
+      <color rgb="00000000"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -484,82 +1093,83 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="29.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="58.375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="29.3796296296296" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22.6296296296296" style="2" customWidth="1"/>
+    <col min="3" max="3" width="58.3796296296296" style="3" customWidth="1"/>
+    <col min="4" max="4" width="11.8796296296296" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
+    <row r="2" s="1" customFormat="1" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1">
-    <sortState ref="A2:D9">
-      <sortCondition descending="1" ref="A1"/>
+  <autoFilter ref="A1:D3">
+    <sortState ref="A1:D3">
+      <sortCondition ref="A1" descending="1"/>
     </sortState>
+    <extLst/>
   </autoFilter>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/408/OS/2024/ModularAutomation/reports/testcases_test.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/testcases_test.xlsx
@@ -69,22 +69,18 @@
     <t>/cgi-bin/luci/api/cmd</t>
   </si>
   <si>
-    <t>devSta.set</t>
+    <t>devConfig.set</t>
   </si>
   <si>
     <t>{
-    "module":"wifi_deassociation",
-    "noParse":true,
-    "async":null,
-    "remoteIp":false,
-    "data":{
-        "user":"hacker",
-        "macs":[
-            "66:77:88:99:AA:BB",
-            "CC:DD:EE:FF:00:11"
-        ]
+    "module": "lwswitch",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "false"
     },
-    "device":"pc"
+    "device": "pc"
 }</t>
   </si>
   <si>
@@ -104,7 +100,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,13 +257,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>

--- a/408/OS/2024/ModularAutomation/reports/testcases_test.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/testcases_test.xlsx
@@ -10,7 +10,7 @@
     <sheet name="#TEMP" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TEMP'!$A$1:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'#TEMP'!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="40">
   <si>
     <t>接口</t>
   </si>
@@ -69,7 +69,263 @@
     <t>/cgi-bin/luci/api/cmd</t>
   </si>
   <si>
+    <t>devSta.set</t>
+  </si>
+  <si>
+    <t>{
+    "module": "uu_acc",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "option": "onoff",
+        "enable": "true"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>#results↓</t>
+  </si>
+  <si>
+    <t>{
+    "module": "rcgame",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enabled": "false",
+        "device_list": [],
+        "loss": "100%",
+        "study": "off",
+        "mtkhnat": "1",
+        "delay_pro": "0%",
+        "game_port": "open",
+        "games": [],
+        "switch_game": "off",
+        "device": "off",
+        "switch_game_list": [],
+        "loss_pro": "0%",
+        "game": "off",
+        "delay": "1000ms",
+        "flowctrl": "0"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "rlog_module_info",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "test": "111"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>devSta.get</t>
+  </si>
+  <si>
+    <t>{
+    "module": "rlog_module_enable",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "module": "sta"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module":"networkConnect",
+    "noParse":true,
+    "async":null,
+    "remoteIp":false,
+    "data":{
+        "ifname":"ifname"
+    },
+    "device":"pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "host_access_delay",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "hostname": "www.baidu.com"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>devSta.del</t>
+  </si>
+  <si>
+    <t>{
+    "module": "enetCap",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "caps": "x",
+        "module": "x"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
     <t>devConfig.set</t>
+  </si>
+  <si>
+    <t>{
+    "module": "pptp_client",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "tunnelname": "pptpflagthn",
+        "username": "",
+        "password": "",
+        "intf_binding": "WAN",
+        "lns": "",
+        "remotesubnet": "",
+        "remotesubnetArr": [
+            "192.168.110.0/24"
+        ],
+        "redirect_gateway": "0",
+        "workmode": "nat",
+        "lcpechointerval": "10",
+        "local_ip": "",
+        "enable": "0",
+        "mppe": "0"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "pptp_server",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "0",
+        "version": "1.0.0",
+        "configId": "0",
+        "configTime": "0",
+        "currentTime": "0"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "child_guard",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "guardPolicy": [
+            {
+                "name": "be:26:03:4d:75:88_child_guard",
+                "auditPolicy": {
+                    "urlFbtEnable": "0",
+                    "appFbtList": [
+                        "Video"
+                    ],
+                    "subAppFbtList": [
+                        {
+                            "list": [],
+                            "type": "Video"
+                        },
+                        {
+                            "type": "Communication",
+                            "list": [
+                                "豆瓣"
+                            ]
+                        }
+                    ],
+                    "urlFbtList": []
+                }
+            },
+            {
+                "name": "be:26:03:ff:ff:88_child_guard",
+                "auditPolicy": {
+                    "urlFbtEnable": "0",
+                    "appFbtList": [
+                        "Video"
+                    ],
+                    "subAppFbtList": [
+                        {
+                            "list": [],
+                            "type": "Video"
+                        },
+                        {
+                            "type": "Communication",
+                            "list": [
+                                "豆瓣",
+                                "小红书"
+                            ]
+                        }
+                    ],
+                    "urlFbtList": []
+                }
+            }
+        ],
+        "guardUser": [
+            {
+                "mac": "be:26:03:4d:75:88",
+                "name": "Redmi-K60",
+                "policy": "be:26:03:4d:75:88_child_guard",
+                "pause": "0",
+                "disconnect": "0"
+            },
+            {
+                "mac": "be:26:03:ff:ff:88",
+                "name": "Redmi-K60tttttest",
+                "policy": "be:26:03:ff:ff:88_child_guard",
+                "pause": "0",
+                "disconnect": "0"
+            }
+        ]
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "igmpproxy",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "0",
+        "version": "1.0.0",
+        "configId": "0",
+        "configTime": "0",
+        "currentTime": "0"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "config_retain",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "config_retain": "x"
+    },
+    "device": "pc"
+}</t>
   </si>
   <si>
     <t>{
@@ -84,7 +340,202 @@
 }</t>
   </si>
   <si>
-    <t>#results↓</t>
+    <t>acConfig.set</t>
+  </si>
+  <si>
+    <t>{
+    "module": "timezone",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "timezone": "CST+8",
+        "zonename": "Asia\/Shanghai",
+        "networkId": "dev_F0:74:8D:5D:02:C4_1717491802",
+        "groupId": "0",
+        "subConfigId": "1717491822_G1SK4AR000416",
+        "version": "1.0.0",
+        "configId": "0",
+        "configTime": "0",
+        "currentTime": "0"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module":"gamng",
+    "noParse":false,
+    "async":null,
+    "remoteIp":false,
+    "data":{
+        "name":"ybb_acc",
+        "option":"install"
+    },
+    "device":"pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "rlog_config",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "0",
+        "tarsaveAll": "1"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "pptp_lcp_client_interval",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "lcpechointerval": "20"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "rlog_module_config",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "total": 1,
+        "module_list": [
+            {
+                "module_name": "system1231232222",
+                "single": 0,
+                "upload_period": 300,
+                "server": "http://cloudloge.rj.link:6222/macclog/log/upload ",
+                "create_period": 10,
+                "file": "x",
+                "protocol": "http",
+                "header": "Content-Type:application/json;charset=UTF-8"
+            }
+        ]
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "wirelessMacFilter",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "version": "1.0.0",
+        "networkId": "dev_00:D0:F8:E3:08:49_1693561441",
+        "groupId": "0",
+        "type": "allow",
+        "macList": [],
+        "axMacList": []
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "mesh_status",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "enable": "true"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "apselect",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "apselect_list": [
+            {
+                "sel_ap": "auto",
+                "sel_band": "2.4G",
+                "mac": "50:3d:c6:96:7d:45"
+            }
+        ]
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "firmware_exist",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "user": "xxx"
+    },
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "eweb_menu",
+    "noParse": false,
+    "async": null,
+    "remoteIp": false,
+    "data": {},
+    "device": "pc"
+}</t>
+  </si>
+  <si>
+    <t>/cgi-bin/luci/api/auth</t>
+  </si>
+  <si>
+    <t>login</t>
+  </si>
+  <si>
+    <t>{
+    "password": "总之是错误的密码",
+    "username": "admin",
+    "time": "1712643931",
+    "encry": true,
+    "limit": false,
+    "setInit": true
+}</t>
+  </si>
+  <si>
+    <t>{
+    "module": "repeater_hostrouter",
+    "noParse": true,
+    "async": null,
+    "remoteIp": false,
+    "data": {
+        "network": "xxx",
+        "repeater": {
+            "radio": "2.4G",
+            "ssid": "123",
+            "channel": "36",
+            "enable": "true",
+            "bssid": "58:69:ab:31:1b:93",
+            "authMode": "OPEN",
+            "encrypType": "NONE",
+            "ssidEncode": "gbk"
+        },
+        "repeater_5g": {
+            "radio": "5G",
+            "enable": "true"
+        },
+        "mode": "wisp",
+        "radop": "5G"
+    },
+    "device": "pc"
+}</t>
   </si>
   <si>
     <t>#END_OF_COL</t>
@@ -100,7 +551,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,6 +562,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -584,141 +1041,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -732,6 +1192,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1088,71 +1551,411 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="4"/>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="29.3796296296296" style="2" customWidth="1"/>
-    <col min="2" max="2" width="22.6296296296296" style="2" customWidth="1"/>
-    <col min="3" max="3" width="58.3796296296296" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11.8796296296296" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="29.3796296296296" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22.6296296296296" style="3" customWidth="1"/>
+    <col min="3" max="3" width="58.3796296296296" style="4" customWidth="1"/>
+    <col min="4" max="4" width="11.8796296296296" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="39.95" customHeight="1" spans="1:5">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="5" t="s">
+      <c r="E2" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="39.95" customHeight="1" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D3">
-    <sortState ref="A1:D3">
+  <autoFilter ref="A1:D27">
+    <sortState ref="A1:D27">
       <sortCondition ref="A1" descending="1"/>
     </sortState>
     <extLst/>

--- a/408/OS/2024/ModularAutomation/reports/testcases_test.xlsx
+++ b/408/OS/2024/ModularAutomation/reports/testcases_test.xlsx
@@ -69,26 +69,66 @@
     <t>/cgi-bin/luci/api/cmd</t>
   </si>
   <si>
-    <t>acConfig.set</t>
+    <t>devConfig.set</t>
   </si>
   <si>
     <t>{
-    "module": "timezone",
+    "module": "network",
     "noParse": false,
+    "remoteIp": false,
+    "device": "pc",
     "async": null,
-    "remoteIp": false,
     "data": {
-        "timezone": "CST+8",
-        "zonename": "Asia\/Shanghai",
-        "networkId": "dev_F0:74:8D:5D:02:C4_1717491802",
-        "groupId": "0",
-        "subConfigId": "1717491822_G1SK4AR000416",
+        "wan": [
+            {
+                "dnsType": "auto",
+                "proto": "pppoe",
+                "dns": "100.0.0.1",
+                "mtu": "1280",
+                "service": "1",
+                "vlanid": "",
+                "password": "xB3$Eavt",
+                "lcp_echo_interval": "30",
+                "lcp_echo_failure": "6",
+                "macaddr": "00:2D:12:45:85:26",
+                "username": "stefan@scoop",
+                "tag": "-1"
+            }
+        ],
+        "lan": [
+            {
+                "macaddr": "10:82:3d:f4:32:9e",
+                "leasetime": "30",
+                "ipstart": "192.168.110.1",
+                "proto": "static",
+                "lastaddr": "192.168.110.1",
+                "ipaddr": "192.168.110.1",
+                "vlanid": "233",
+                "ignore": "0",
+                "netmask": "255.255.255.0",
+                "limit": "254",
+                "conflict": "false"
+            },
+            {
+                "macaddr": "10:82:3D:D5:20:54",
+                "leasetime": "480",
+                "ipstart": "192.168.12.1",
+                "lastaddr": "192.168.12.254",
+                "hasReturnRouter": false,
+                "ipaddr": "192.168.12.1",
+                "dhcpServerDevice": "",
+                "vlanid": "12",
+                "ignore": "0",
+                "netmask": "255.255.255.0",
+                "limit": "254",
+                "pool": "EGW",
+                "desc": "22ttttt''"
+            }
+        ],
         "version": "1.0.0",
-        "configId": "0",
-        "configTime": "0",
-        "currentTime": "0"
-    },
-    "device": "pc"
+        "wanNum": "1",
+        "lanNum": "2"
+    }
 }</t>
   </si>
   <si>
@@ -1156,7 +1196,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D3">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D3" etc:filterBottomFollowUsedRange="0">
     <sortState ref="A1:D3">
       <sortCondition ref="A1" descending="1"/>
     </sortState>
